--- a/data/manufacturing/RAGFlow_피스톤로드_가공_오류DB.xlsx
+++ b/data/manufacturing/RAGFlow_피스톤로드_가공_오류DB.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="출처" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5169,8 +5169,1209 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(0/-0.032)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 끼워맞춤 축 Ø300(0/-0.032)을 버니어 캘리퍼스로 재서 합격 처리</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭이 0.032mm(32µm)인 맞춤 돌기를 버니어 캘리퍼스(최소 눈금 0.02mm, 기기 오차 ±0.03mm 수준)로 재서 300.00으로 기록하고 합격 처리했다. 마이크로미터로 다시 재니 300.008로 상한(300.000)을 넘었다.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭보다 오차가 큰 측정기 사용</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 공차는 공차 폭의 1/10 이하 분해능(0.001mm)인 외측 마이크로미터로 잰다. 캘리퍼스는 황삭 여유 확인에만 쓴다.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>외측 마이크로미터(0.001mm), 기준봉</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭이 0.05mm 이하인 끼워맞춤 축</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>일반공차 치수는 제외</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>측정기</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>피스톤헤드 조립 시 억지로 들어가거나 안 들어감</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>외측 마이크로미터로 재측정, 같은 로트 재확인</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, A측 맞춤 돌기, 외경, DIMENSION, Ø300(0/-0.032), 공차 폭보다 오차가 큰 측정기 사용, A측 맞춤 돌기, C4 측정기, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-035] 부품: 피스톤 로드. 부위: A측 맞춤 돌기. 형상: A측 맞춤 돌기(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(0/-0.032). 오류 유형: C4 측정기. 중요도: 상. 오류: [정삭] 끼워맞춤 축 Ø300(0/-0.032)을 버니어 캘리퍼스로 재서 합격 처리. 상황: 공차 폭이 0.032mm(32µm)인 맞춤 돌기를 버니어 캘리퍼스(최소 눈금 0.02mm, 기기 오차 ±0.03mm 수준)로 재서 300.00으로 기록하고 합격 처리했다. 마이크로미터로 다시 재니 300.008로 상한(300.000)을 넘었다. 원인: 공차 폭보다 오차가 큰 측정기 사용. 주의사항: 끼워맞춤 공차는 공차 폭의 1/10 이하 분해능(0.001mm)인 외측 마이크로미터로 잰다. 캘리퍼스는 황삭 여유 확인에만 쓴다. 조치: 외측 마이크로미터로 재측정, 같은 로트 재확인. 영향: 피스톤헤드 조립 시 억지로 들어가거나 안 들어감. 발생 단계: 정삭 후. 적용 조건: 공차 폭이 0.05mm 이하인 끼워맞춤 축. 제외·확인 조건: 일반공차 치수는 제외. 측정기 후보: 외측 마이크로미터(0.001mm), 기준봉. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(0/-0.032)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 편측 공차 (0/-0.032)를 ±0.032로 보고 300.01을 합격 처리</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>도면 Ø300(0/-0.032)은 299.968~300.000만 합격인데, 작업자가 '300 ±0.032'로 읽어 300.010을 합격으로 기록했다. 축의 상한은 기준치수 300.000이다.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>편측 공차 방향 해석 오류</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>괄호 안 앞 숫자가 상한, 뒤 숫자가 하한이다. 화면의 허용 범위(최소~최대)를 숫자로 확인하고 판정한다.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>외측 마이크로미터</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>(0/−) 또는 (+/0) 편측 공차가 붙은 치수</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>±대칭 공차는 제외</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 불량(억지 끼움), 조립 불가</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>허용 범위로 재판정, 재가공 여부 결정</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, A측 맞춤 돌기, 외경, DIMENSION, Ø300(0/-0.032), 편측 공차 방향 해석 오류, A측 맞춤 돌기, C3 도면 해석, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-036] 부품: 피스톤 로드. 부위: A측 맞춤 돌기. 형상: A측 맞춤 돌기(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(0/-0.032). 오류 유형: C3 도면 해석. 중요도: 상. 오류: [정삭] 편측 공차 (0/-0.032)를 ±0.032로 보고 300.01을 합격 처리. 상황: 도면 Ø300(0/-0.032)은 299.968~300.000만 합격인데, 작업자가 '300 ±0.032'로 읽어 300.010을 합격으로 기록했다. 축의 상한은 기준치수 300.000이다. 원인: 편측 공차 방향 해석 오류. 주의사항: 괄호 안 앞 숫자가 상한, 뒤 숫자가 하한이다. 화면의 허용 범위(최소~최대)를 숫자로 확인하고 판정한다. 조치: 허용 범위로 재판정, 재가공 여부 결정. 영향: 끼워맞춤 불량(억지 끼움), 조립 불가. 발생 단계: 정삭 후. 적용 조건: (0/−) 또는 (+/0) 편측 공차가 붙은 치수. 제외·확인 조건: ±대칭 공차는 제외. 측정기 후보: 외측 마이크로미터. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(0/-0.032)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭 직후 따뜻한 맞춤 돌기를 재서 끼워맞춤 공차 절반이 온도로 사라짐</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>연삭 직후 표면이 측정실보다 5℃ 높은 상태에서 Ø300을 재서 299.990(합격)으로 기록했다. 강은 Ø300에서 5℃당 약 0.017mm 커지므로, 식은 뒤에는 299.973 근처로 하한 가까이 떨어진다.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤면 온도 보정 누락</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭이 좁은 끼워맞춤면은 표면 온도를 함께 기록하고, 측정실 온도(20℃)와 2℃ 이상 차이 나면 식힌 뒤 다시 잰다.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>외측 마이크로미터, 표면 온도계</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>연삭·정삭 직후 끼워맞춤면 측정</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 측정한 경우 제외</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>A측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>온도·환경</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>합격 판정 후 실제 치수가 하한 근처 또는 이탈</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>냉각 후 재측정, 온도 함께 기록</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, A측 맞춤 돌기, 외경, DIMENSION, Ø300(0/-0.032), 끼워맞춤면 온도 보정 누락, A측 맞춤 돌기, C9 온도·환경, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-037] 부품: 피스톤 로드. 부위: A측 맞춤 돌기. 형상: A측 맞춤 돌기(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(0/-0.032). 오류 유형: C9 온도·환경. 중요도: 중. 오류: [정삭] 연삭 직후 따뜻한 맞춤 돌기를 재서 끼워맞춤 공차 절반이 온도로 사라짐. 상황: 연삭 직후 표면이 측정실보다 5℃ 높은 상태에서 Ø300을 재서 299.990(합격)으로 기록했다. 강은 Ø300에서 5℃당 약 0.017mm 커지므로, 식은 뒤에는 299.973 근처로 하한 가까이 떨어진다. 원인: 끼워맞춤면 온도 보정 누락. 주의사항: 공차 폭이 좁은 끼워맞춤면은 표면 온도를 함께 기록하고, 측정실 온도(20℃)와 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 조치: 냉각 후 재측정, 온도 함께 기록. 영향: 합격 판정 후 실제 치수가 하한 근처 또는 이탈. 발생 단계: 정삭 후. 적용 조건: 연삭·정삭 직후 끼워맞춤면 측정. 제외·확인 조건: 온도 안정 후 측정한 경우 제외. 측정기 후보: 외측 마이크로미터, 표면 온도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>B측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Ø300(0/-0.032)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] B측 맞춤 돌기를 한 단면·한 방향만 재서 테이퍼·타원을 놓침</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>크로스헤드 Ø300 구멍에 들어가는 B측 맞춤 돌기를 끝단 한 곳에서 한 방향만 재서 합격 처리했다. 뿌리 쪽은 299.962로 하한을 벗어나 있었다.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 길이 전체 확인 누락</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 면은 끼워지는 길이의 양 끝 2단면 × 직각 2방향(4점)을 재고, 가장 큰 값과 작은 값을 모두 기록한다.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>외측 마이크로미터</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 축 정삭 후</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>B측 맞춤 돌기</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>측정 위치</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>크로스헤드 조립 시 한쪽 헐거움</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>4점 재측정, 범위 밖이면 재연삭</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, B측 맞춤 돌기, 외경, DIMENSION, Ø300(0/-0.032), 끼워맞춤 길이 전체 확인 누락, B측 맞춤 돌기, C1 측정 위치, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-038] 부품: 피스톤 로드. 부위: B측 맞춤 돌기. 형상: B측 맞춤 돌기(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø300(0/-0.032). 오류 유형: C1 측정 위치. 중요도: 중. 오류: [정삭] B측 맞춤 돌기를 한 단면·한 방향만 재서 테이퍼·타원을 놓침. 상황: 크로스헤드 Ø300 구멍에 들어가는 B측 맞춤 돌기를 끝단 한 곳에서 한 방향만 재서 합격 처리했다. 뿌리 쪽은 299.962로 하한을 벗어나 있었다. 원인: 끼워맞춤 길이 전체 확인 누락. 주의사항: 끼워맞춤 면은 끼워지는 길이의 양 끝 2단면 × 직각 2방향(4점)을 재고, 가장 큰 값과 작은 값을 모두 기록한다. 조치: 4점 재측정, 범위 밖이면 재연삭. 영향: 크로스헤드 조립 시 한쪽 헐거움. 발생 단계: 정삭 후. 적용 조건: 끼워맞춤 축 정삭 후. 제외·확인 조건: 없음. 측정기 후보: 외측 마이크로미터. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Ø400</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>공정</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[중삭] 중삭 떨림 자국을 연삭 여유 0.5mm로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>긴 몸체 중삭 중 방진구 위치가 멀어 떨림 자국(채터)이 생겼는데, 치수는 중삭 목표 범위라 그대로 넘겼다. 연삭 후에도 자국이 남아 R1(Ra 0.4)을 만족하지 못했다.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>중삭 표면 상태 확인 누락</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>중삭 후에는 치수와 함께 떨림 자국·깊은 이송 자국이 없는지 눈과 손으로 확인한다. 자국이 있으면 방진구 위치를 바꿔 다시 중삭한다.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>육안·촉감 확인, 대형 외측 마이크로미터</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>정삭에서 Ra 0.8 이하를 요구하는 면의 중삭 후</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>조도 요구가 없는 면은 기록만 함</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>공정 추세·시삭</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>중삭 후</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>정삭 후 조도 불합격, 재연삭·치수 부족 위험</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>방진구 위치 변경 후 재중삭</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 로드 본체, 외경, DIMENSION, Ø400, 중삭 표면 상태 확인 누락, 로드 본체, C12 공정 추세·시삭, 중삭 후</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-039] 부품: 피스톤 로드. 부위: 로드 본체. 형상: 로드 본체(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø400. 오류 유형: C12 공정 추세·시삭. 중요도: 상. 오류: [중삭] 중삭 떨림 자국을 연삭 여유 0.5mm로 지울 수 있다고 보고 넘김. 상황: 긴 몸체 중삭 중 방진구 위치가 멀어 떨림 자국(채터)이 생겼는데, 치수는 중삭 목표 범위라 그대로 넘겼다. 연삭 후에도 자국이 남아 R1(Ra 0.4)을 만족하지 못했다. 원인: 중삭 표면 상태 확인 누락. 주의사항: 중삭 후에는 치수와 함께 떨림 자국·깊은 이송 자국이 없는지 눈과 손으로 확인한다. 자국이 있으면 방진구 위치를 바꿔 다시 중삭한다. 조치: 방진구 위치 변경 후 재중삭. 영향: 정삭 후 조도 불합격, 재연삭·치수 부족 위험. 발생 단계: 중삭 후. 적용 조건: 정삭에서 Ra 0.8 이하를 요구하는 면의 중삭 후. 제외·확인 조건: 조도 요구가 없는 면은 기록만 함. 측정기 후보: 육안·촉감 확인, 대형 외측 마이크로미터. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭면 조도를 연삭 줄무늬와 같은 방향으로 재서 Ra가 낮게 나옴</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체 연삭면(R1 = Ra 0.4)을 원주 방향(연삭 줄무늬와 평행)으로 재서 Ra 0.15로 합격 처리했다. 축 방향(줄무늬에 직각)으로 다시 재니 Ra 0.52였다.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 방향 오류</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>조도는 가공 줄무늬에 직각 방향으로 잰다. 원통 연삭면은 축 방향으로 촉침을 움직인다.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계(촉침식)</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>연삭·선삭 정삭면 조도 측정</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>줄무늬 방향이 없는 면(래핑 등)은 제외</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>측정 방법</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>조도 불량 면이 합격 처리, 패킹·실 마모</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>직각 방향으로 재측정</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 로드 본체, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.4), 조도 측정 방향 오류, 로드 본체, C5 측정 방법, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-040] 부품: 피스톤 로드. 부위: 로드 본체. 형상: 로드 본체(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.4). 오류 유형: C5 측정 방법. 중요도: 상. 오류: [정삭] 연삭면 조도를 연삭 줄무늬와 같은 방향으로 재서 Ra가 낮게 나옴. 상황: 로드 본체 연삭면(R1 = Ra 0.4)을 원주 방향(연삭 줄무늬와 평행)으로 재서 Ra 0.15로 합격 처리했다. 축 방향(줄무늬에 직각)으로 다시 재니 Ra 0.52였다. 원인: 조도 측정 방향 오류. 주의사항: 조도는 가공 줄무늬에 직각 방향으로 잰다. 원통 연삭면은 축 방향으로 촉침을 움직인다. 조치: 직각 방향으로 재측정. 영향: 조도 불량 면이 합격 처리, 패킹·실 마모. 발생 단계: 정삭 후. 적용 조건: 연삭·선삭 정삭면 조도 측정. 제외·확인 조건: 줄무늬 방향이 없는 면(래핑 등)은 제외. 측정기 후보: 표면조도계(촉침식). 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 조도계 컷오프를 0.25mm로 둔 채 Ra 0.4 면을 측정</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>이전 작업(정밀 래핑면)에 쓰던 컷오프 0.25mm 설정을 그대로 두고 Ra 0.4 연삭면을 재서 Ra 0.28로 기록했다. Ra 0.1~2 범위는 컷오프 0.8mm, 평가 길이 4mm가 기본이다.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>조도계 설정 확인 누락</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>측정 전 컷오프(λc)·평가 길이를 도면 Ra 값에 맞는지 확인한다 (Ra 0.1~2 → 0.8mm). 기준 시편으로 조도계를 먼저 확인한다.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계, 조도 기준 시편</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>조도계 설정을 바꿔 쓰는 경우</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>측정기</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>조도 과소 판정</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>설정 확인 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 로드 본체, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.4), 조도계 설정 확인 누락, 로드 본체, C4 측정기, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-041] 부품: 피스톤 로드. 부위: 로드 본체. 형상: 로드 본체(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.4). 오류 유형: C4 측정기. 중요도: 중. 오류: [정삭] 조도계 컷오프를 0.25mm로 둔 채 Ra 0.4 면을 측정. 상황: 이전 작업(정밀 래핑면)에 쓰던 컷오프 0.25mm 설정을 그대로 두고 Ra 0.4 연삭면을 재서 Ra 0.28로 기록했다. Ra 0.1~2 범위는 컷오프 0.8mm, 평가 길이 4mm가 기본이다. 원인: 조도계 설정 확인 누락. 주의사항: 측정 전 컷오프(λc)·평가 길이를 도면 Ra 값에 맞는지 확인한다 (Ra 0.1~2 → 0.8mm). 기준 시편으로 조도계를 먼저 확인한다. 조치: 설정 확인 후 재측정. 영향: 조도 과소 판정. 발생 단계: 정삭 후. 적용 조건: 조도계 설정을 바꿔 쓰는 경우. 제외·확인 조건: 없음. 측정기 후보: 표면조도계, 조도 기준 시편. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PLANE</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>A측 플랜지</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>R2 (= Ra 1.6)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R2를 반지름 2mm 치수로 읽고 R 게이지로 확인</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>A측 플랜지 맞춤면 옆의 'R2'를 반지름 치수로 보고 R 게이지로 모서리 반지름을 재서 기록했다. 표제란 범례상 R2는 표면 거칠기 Ra 1.6이었다.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>조도 기호와 반지름 치수 혼동</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>이 도면의 R1·R2는 표제란 범례(R1 = Ra 0.4, R2 = Ra 1.6)의 조도 기호다. 삼각형 조도 기호에 붙은 R1·R2는 반지름이 아니다. 관리자 검토 화면의 분류(조도)를 확인한다.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>조도를 범례 기호(R1, R2)로 표기한 도면</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>실제 모서리 반지름 치수(R500 등)는 제외</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>A측 플랜지</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>조도 미측정, 엉뚱한 항목 기록</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>조도계로 Ra 측정 후 기록 수정</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>OCR은 R1을 Ri로 읽기도 하고, R1·R2를 반지름 치수로 분류한다</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>PLANE, A측 플랜지, 표면 거칠기, SURFACE_ROUGHNESS, R2 (= Ra 1.6), 조도 기호와 반지름 치수 혼동, A측 플랜지, C3 도면 해석, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-042] 부품: 피스톤 로드. 부위: A측 플랜지. 형상: A측 플랜지(PLANE). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R2 (= Ra 1.6). 오류 유형: C3 도면 해석. 중요도: 중. 오류: [공통] 조도 기호 R2를 반지름 2mm 치수로 읽고 R 게이지로 확인. 상황: A측 플랜지 맞춤면 옆의 'R2'를 반지름 치수로 보고 R 게이지로 모서리 반지름을 재서 기록했다. 표제란 범례상 R2는 표면 거칠기 Ra 1.6이었다. 원인: 조도 기호와 반지름 치수 혼동. 주의사항: 이 도면의 R1·R2는 표제란 범례(R1 = Ra 0.4, R2 = Ra 1.6)의 조도 기호다. 삼각형 조도 기호에 붙은 R1·R2는 반지름이 아니다. 관리자 검토 화면의 분류(조도)를 확인한다. 조치: 조도계로 Ra 측정 후 기록 수정. 영향: 조도 미측정, 엉뚱한 항목 기록. 발생 단계: 가공 공통. 적용 조건: 조도를 범례 기호(R1, R2)로 표기한 도면. 제외·확인 조건: 실제 모서리 반지름 치수(R500 등)는 제외. 측정기 후보: 표면조도계. OCR 참고: OCR은 R1을 Ri로 읽기도 하고, R1·R2를 반지름 치수로 분류한다. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>PR-M-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>피스톤 로드</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭액·기름막이 남은 면에서 조도를 재서 값이 튐</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>연삭 직후 연삭액이 남은 몸체에서 조도를 재서 측정마다 Ra가 0.3~0.6으로 달라졌고, 가장 작은 값을 기록했다.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>측정면 세척 누락</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 전 측정 부위를 세척제로 닦고 마른 상태에서 잰다. 같은 위치를 3회 재서 평균과 범위를 기록한다.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계, 세척제</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>연삭·호닝 직후 조도 측정</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>로드 본체</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>부품 상태</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>조도 오판정</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>세척 후 3회 재측정</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 로드 본체, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.4), 측정면 세척 누락, 로드 본체, C6 부품 상태, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 PR-M-043] 부품: 피스톤 로드. 부위: 로드 본체. 형상: 로드 본체(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.4). 오류 유형: C6 부품 상태. 중요도: 중. 오류: [정삭] 연삭액·기름막이 남은 면에서 조도를 재서 값이 튐. 상황: 연삭 직후 연삭액이 남은 몸체에서 조도를 재서 측정마다 Ra가 0.3~0.6으로 달라졌고, 가장 작은 값을 기록했다. 원인: 측정면 세척 누락. 주의사항: 조도 측정 전 측정 부위를 세척제로 닦고 마른 상태에서 잰다. 같은 위치를 3회 재서 평균과 범위를 기록한다. 조치: 세척 후 3회 재측정. 영향: 조도 오판정. 발생 단계: 정삭 후. 적용 조건: 연삭·호닝 직후 조도 측정. 제외·확인 조건: 없음. 측정기 후보: 표면조도계, 세척제. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA35"/>
+  <autoFilter ref="A1:AA44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5181,7 +6382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5784,6 +6985,159 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PR-M-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[정삭] 끼워맞춤 축 Ø300(0/-0.032)을 버니어 캘리퍼스로 재서 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PR-M-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[정삭] 편측 공차 (0/-0.032)를 ±0.032로 보고 300.01을 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PR-M-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭 직후 따뜻한 맞춤 돌기를 재서 끼워맞춤 공차 절반이 온도로 사라짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PR-M-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[정삭] B측 맞춤 돌기를 한 단면·한 방향만 재서 테이퍼·타원을 놓침</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PR-M-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[중삭] 중삭 떨림 자국을 연삭 여유 0.5mm로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PR-M-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭면 조도를 연삭 줄무늬와 같은 방향으로 재서 Ra가 낮게 나옴</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PR-M-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[정삭] 조도계 컷오프를 0.25mm로 둔 채 Ra 0.4 면을 측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PR-M-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R2를 반지름 2mm 치수로 읽고 R 게이지로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PR-M-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_PR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[정삭] 연삭액·기름막이 남은 면에서 조도를 재서 값이 튐</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
